--- a/output/pdf_financials_xlsx/ENI.UN.xlsx
+++ b/output/pdf_financials_xlsx/ENI.UN.xlsx
@@ -431,6 +431,16 @@
   </sheetPr>
   <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ENI.UN.xlsx
+++ b/output/pdf_financials_xlsx/ENI.UN.xlsx
@@ -631,7 +631,7 @@
         <v>0.168901</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.11308</v>
+        <v>0.175324</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>0.168901</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.11308</v>
+        <v>0.175324</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -4821,7 +4821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6846,7 +6846,11 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -9859,7 +9863,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Transaction costs (17,956)</t>
+          <t>Transaction costs                                            (17,956)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9908,7 +9912,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Transaction costs (17,956)</t>
+          <t>Transaction costs                                            (17,956)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10001,17 +10005,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>(b) Description of the Fund</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>The financial statements were authorized for issue by Artemis Investment Management Limited on March</t>
+          <t>Dividends $</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -10021,10 +10025,10 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.002018</v>
+        <v>0.35761</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2e-05</v>
+        <v>0.417954</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -10036,15 +10040,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J107" s="5" t="n">
+        <v>0.275478</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0.11517</v>
       </c>
     </row>
     <row r="108">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dividends $</t>
+          <t>Interest income for distribution purposes</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.35761</v>
+        <v>0.005708</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.417954</v>
+        <v>0.004965</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0.275478</v>
+        <v>0.0005</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>0.11517</v>
+        <v>3.3e-05</v>
       </c>
     </row>
     <row r="109">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Interest income for distribution purposes</t>
+          <t>Foreign exchange gain on cash</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -10114,11 +10114,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="5" t="n">
-        <v>0.005708</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>0.004965</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -10131,10 +10135,10 @@
         </is>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.003505</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>3.3e-05</v>
+        <v>0.015118</v>
       </c>
     </row>
     <row r="110">
@@ -10150,24 +10154,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on cash</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Net realized gain (loss) on sale of investments</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetRealizedGainLossOnInvestments</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>-2.817144</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.276592</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -10180,10 +10184,10 @@
         </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0.003505</v>
+        <v>-0.227739</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0.015118</v>
+        <v>0.163466</v>
       </c>
     </row>
     <row r="111">
@@ -10199,24 +10203,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on sale of investments</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
+          <t>Change in unrealized appreciation on investments</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>-2.817144</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0.276592</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -10229,10 +10233,10 @@
         </is>
       </c>
       <c r="J111" s="5" t="n">
-        <v>-0.227739</v>
+        <v>0.360511</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>0.163466</v>
+        <v>0.199324</v>
       </c>
     </row>
     <row r="112">
@@ -10248,7 +10252,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Change in unrealized appreciation on investments</t>
+          <t>Income total</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -10257,15 +10261,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="5" t="n">
+        <v>3.011722</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-0.353948</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0.360511</v>
+        <v>0.412255</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>0.199324</v>
+        <v>0.493111</v>
       </c>
     </row>
     <row r="113">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Income total</t>
+          <t>Administrative (note 8)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -10306,11 +10306,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>3.011722</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>-0.353948</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -10323,10 +10327,10 @@
         </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.412255</v>
+        <v>0.081147</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.493111</v>
+        <v>0.088153</v>
       </c>
     </row>
     <row r="114">
@@ -10342,10 +10346,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Administrative (note 8)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Management fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -10372,10 +10380,10 @@
         </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0.081147</v>
+        <v>0.048706</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>0.088153</v>
+        <v>0.046648</v>
       </c>
     </row>
     <row r="115">
@@ -10391,14 +10399,10 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Management fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Unitholder servicing fees</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -10425,10 +10429,10 @@
         </is>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0.048706</v>
+        <v>0.047647</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>0.046648</v>
+        <v>0.057511</v>
       </c>
     </row>
     <row r="116">
@@ -10444,7 +10448,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unitholder servicing fees</t>
+          <t>Custody, valuation and transfer fees</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -10474,10 +10478,10 @@
         </is>
       </c>
       <c r="J116" s="5" t="n">
-        <v>0.047647</v>
+        <v>0.032692</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>0.057511</v>
+        <v>0.015499</v>
       </c>
     </row>
     <row r="117">
@@ -10493,7 +10497,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Custody, valuation and transfer fees</t>
+          <t>Audit and review fees</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -10523,10 +10527,10 @@
         </is>
       </c>
       <c r="J117" s="5" t="n">
-        <v>0.032692</v>
+        <v>0.030138</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0.015499</v>
+        <v>0.050001</v>
       </c>
     </row>
     <row r="118">
@@ -10542,7 +10546,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Audit and review fees</t>
+          <t>Independent review committee fees</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -10572,10 +10576,10 @@
         </is>
       </c>
       <c r="J118" s="5" t="n">
-        <v>0.030138</v>
+        <v>0.030082</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0.050001</v>
+        <v>0.029999</v>
       </c>
     </row>
     <row r="119">
@@ -10591,7 +10595,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Independent review committee fees</t>
+          <t>Regulatory and listing fees</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -10624,7 +10628,7 @@
         <v>0.030082</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>0.029999</v>
+        <v>0.029998</v>
       </c>
     </row>
     <row r="120">
@@ -10640,10 +10644,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Regulatory and listing fees</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Investment management fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -10670,10 +10678,10 @@
         </is>
       </c>
       <c r="J120" s="5" t="n">
-        <v>0.030082</v>
+        <v>0.027832</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>0.029998</v>
+        <v>0.026656</v>
       </c>
     </row>
     <row r="121">
@@ -10689,7 +10697,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Investment management fees (note 8)</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10723,10 +10731,10 @@
         </is>
       </c>
       <c r="J121" s="5" t="n">
-        <v>0.027832</v>
+        <v>0.010028</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0.026656</v>
+        <v>0.010001</v>
       </c>
     </row>
     <row r="122">
@@ -10742,14 +10750,10 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10776,10 +10780,10 @@
         </is>
       </c>
       <c r="J122" s="5" t="n">
-        <v>0.010028</v>
+        <v>7.8e-05</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0.010001</v>
+        <v>0.000616</v>
       </c>
     </row>
     <row r="123">
@@ -10795,7 +10799,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Portfolio transaction costs (note 9)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -10825,10 +10829,10 @@
         </is>
       </c>
       <c r="J123" s="5" t="n">
-        <v>7.8e-05</v>
+        <v>0.008387</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>0.000616</v>
+        <v>0.003186</v>
       </c>
     </row>
     <row r="124">
@@ -10844,10 +10848,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portfolio transaction costs (note 9)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10874,10 +10882,10 @@
         </is>
       </c>
       <c r="J124" s="5" t="n">
-        <v>0.008387</v>
+        <v>0.346819</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>0.003186</v>
+        <v>0.358268</v>
       </c>
     </row>
     <row r="125">
@@ -10893,14 +10901,10 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Operating profit before taxes</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10927,10 +10931,10 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>0.346819</v>
+        <v>0.06543599999999999</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>0.358268</v>
+        <v>0.134843</v>
       </c>
     </row>
     <row r="126">
@@ -10946,7 +10950,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Operating profit before taxes</t>
+          <t>Withholding taxes/reclaims</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -10976,10 +10980,10 @@
         </is>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.06543599999999999</v>
+        <v>0.004397</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.134843</v>
+        <v>0.006019</v>
       </c>
     </row>
     <row r="127">
@@ -10990,12 +10994,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Increase in net assets attributable to holders of</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Withholding taxes/reclaims</t>
+          <t>Increase in net assets attributable to holders of redeemable units from operations $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -11025,10 +11029,10 @@
         </is>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.004397</v>
+        <v>0.061039</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.006019</v>
+        <v>0.128824</v>
       </c>
     </row>
     <row r="128">
@@ -11044,7 +11048,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Increase in net assets attributable to holders of redeemable units from operations $</t>
+          <t>Weighted average number of units outstanding</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -11074,10 +11078,10 @@
         </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.061039</v>
+        <v>3.506784</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.128824</v>
+        <v>3.160322</v>
       </c>
     </row>
     <row r="129">
@@ -11093,7 +11097,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Weighted average number of units outstanding</t>
+          <t>Increase in net assets attributable to holders of redeemable units from operations per unit(1) $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -11123,10 +11127,10 @@
         </is>
       </c>
       <c r="J129" s="5" t="n">
-        <v>3.506784</v>
+        <v>2e-08</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>3.160322</v>
+        <v>4e-08</v>
       </c>
     </row>
     <row r="130">
@@ -11137,12 +11141,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Increase in net assets attributable to holders of</t>
+          <t>Net assets attributable to holders of redeemable units,</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Increase in net assets attributable to holders of redeemable units from operations per unit(1) $</t>
+          <t>Net assets attributable to holders of redeemable units, beginning of year $</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -11172,10 +11176,10 @@
         </is>
       </c>
       <c r="J130" s="5" t="n">
-        <v>2e-08</v>
+        <v>7.468117</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>4e-08</v>
+        <v>6.442521</v>
       </c>
     </row>
     <row r="131">
@@ -11186,12 +11190,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units,</t>
+          <t>Increase in net assets attributable to holders of</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units, beginning of year $</t>
+          <t>Increase in net assets attributable to holders of redeemable units from operations</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -11221,10 +11225,10 @@
         </is>
       </c>
       <c r="J131" s="5" t="n">
-        <v>7.468117</v>
+        <v>0.061039</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>6.442521</v>
+        <v>0.128824</v>
       </c>
     </row>
     <row r="132">
@@ -11235,12 +11239,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Increase in net assets attributable to holders of</t>
+          <t>Redeemable unit transactions</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Increase in net assets attributable to holders of redeemable units from operations</t>
+          <t>Reinvested distributions</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -11249,15 +11253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="5" t="n">
+        <v>0.011651</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.012702</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.061039</v>
+        <v>0.012745</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0.128824</v>
+        <v>0.011256</v>
       </c>
     </row>
     <row r="133">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Reinvested distributions</t>
+          <t>Redemption of redeemable units</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.011651</v>
+        <v>-1.172316</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.012702</v>
+        <v>-1.023738</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0.012745</v>
+        <v>-0.679409</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>0.011256</v>
+        <v>-0.667651</v>
       </c>
     </row>
     <row r="134">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Redemption of redeemable units</t>
+          <t>Redeemable unit transactions total</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -11344,10 +11344,10 @@
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-1.172316</v>
+        <v>-1.160665</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>-1.023738</v>
+        <v>-1.011036</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="J134" s="5" t="n">
-        <v>-0.679409</v>
+        <v>-0.666664</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>-0.667651</v>
+        <v>-0.656395</v>
       </c>
     </row>
     <row r="135">
@@ -11374,12 +11374,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Redeemable unit transactions</t>
+          <t>Distributions to holders of redeemable units</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Redeemable unit transactions total</t>
+          <t>Return to holders of redeemable units</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>-1.160665</v>
+        <v>-0.596773</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>-1.011036</v>
+        <v>-0.409504</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>-0.666664</v>
+        <v>-0.419971</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>-0.656395</v>
+        <v>-0.372795</v>
       </c>
     </row>
     <row r="136">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Distributions to holders of redeemable units</t>
+          <t>Net decrease in net assets attributable to</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Return to holders of redeemable units</t>
+          <t>Net decrease in net assets attributable to holders of redeemable units for the year</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -11433,11 +11433,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>-0.596773</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>-0.409504</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -11450,10 +11454,10 @@
         </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>-0.419971</v>
+        <v>-1.025596</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>-0.372795</v>
+        <v>-0.900366</v>
       </c>
     </row>
     <row r="137">
@@ -11464,12 +11468,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Net decrease in net assets attributable to</t>
+          <t>Net assets attributable to holders of redeemable units,</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Net decrease in net assets attributable to holders of redeemable units for the year</t>
+          <t>Net assets attributable to holders of redeemable units, end of year $</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -11499,10 +11503,10 @@
         </is>
       </c>
       <c r="J137" s="5" t="n">
-        <v>-1.025596</v>
+        <v>6.442521</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>-0.900366</v>
+        <v>5.542155</v>
       </c>
     </row>
     <row r="138">
@@ -11518,7 +11522,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units, end of year $</t>
+          <t>Distributions per unit $</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -11548,10 +11552,10 @@
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>6.442521</v>
+        <v>1.2e-07</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>5.542155</v>
+        <v>1.2e-07</v>
       </c>
     </row>
     <row r="139">
@@ -11562,12 +11566,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units,</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Distributions per unit $</t>
+          <t>Foreign exchange loss on cash</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -11576,15 +11580,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F139" s="5" t="n">
+        <v>-0.110573</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>-0.046039</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -11596,11 +11596,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>1.2e-07</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -11616,7 +11620,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Foreign exchange loss on cash</t>
+          <t>Change in unrealized appreciation (depreciation) of investments</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -11626,10 +11630,10 @@
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>-0.110573</v>
+        <v>5.576121</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-0.046039</v>
+        <v>-1.00742</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -11660,25 +11664,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Change in unrealized appreciation (depreciation) of investments</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Management fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
-        <v>5.576121</v>
+        <v>0.097938</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>-1.00742</v>
+        <v>0.091765</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11714,7 +11722,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Management fees (note 8)</t>
+          <t>Investment management fees (note 8)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11728,10 +11736,10 @@
         </is>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.097938</v>
+        <v>0.055964</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.091765</v>
+        <v>0.052437</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11767,24 +11775,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Investment management fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Administrative (note 8)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.055964</v>
+        <v>0.067944</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.052437</v>
+        <v>0.057271</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11820,20 +11824,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Administrative (note 8)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.067944</v>
+        <v>0.014999</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.057271</v>
+        <v>0.031122</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11869,24 +11877,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Regulatory and listing</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>0.014999</v>
+        <v>-0.0086</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>-0.031122</v>
+        <v>-0.038281</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11922,7 +11926,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Regulatory and listing</t>
+          <t>Unitholder servicing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -11932,10 +11936,10 @@
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.055209</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>-0.038281</v>
+        <v>0.012566</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11971,7 +11975,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unitholder servicing</t>
+          <t>Custody, valuation and transfer fees</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -11981,10 +11985,10 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.055209</v>
+        <v>0.008399</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.012566</v>
+        <v>0.022808</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -12020,7 +12024,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Custody, valuation and transfer fees</t>
+          <t>Audit and review fees</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -12030,10 +12034,10 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.008399</v>
+        <v>0.050001</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.022808</v>
+        <v>0.049729</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -12069,7 +12073,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Audit and review fees</t>
+          <t>Independent review committee fees</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -12079,10 +12083,10 @@
         </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.050001</v>
+        <v>0.030001</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.049729</v>
+        <v>0.011732</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -12118,7 +12122,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Independent review committee fees</t>
+          <t>Portfolio transaction costs (note 9)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -12128,10 +12132,10 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.030001</v>
+        <v>0.014478</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.011732</v>
+        <v>0.007212</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -12167,7 +12171,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portfolio transaction costs (note 9)</t>
+          <t>Expenses (income) total</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -12177,10 +12181,10 @@
         </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.014478</v>
+        <v>0.386333</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.007212</v>
+        <v>0.236117</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -12216,7 +12220,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Expenses (income) total</t>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations $</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -12226,10 +12230,10 @@
         </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0.386333</v>
+        <v>2.625389</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.236117</v>
+        <v>-0.590065</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -12265,7 +12269,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations $</t>
+          <t>Weighted average number of units outstanding</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -12275,10 +12279,10 @@
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>2.625389</v>
+        <v>5.017163</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>-0.590065</v>
+        <v>4.588481</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -12314,7 +12318,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Weighted average number of units outstanding</t>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations per unit (1) $</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -12324,10 +12328,10 @@
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>5.017163</v>
+        <v>5.2e-07</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>4.588481</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -12358,12 +12362,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>See accompanying notes to financial statements.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations per unit(1) $</t>
+          <t>Net assets attributable to holders of redeemable units, beginning of year $</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -12373,10 +12377,10 @@
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>5.2e-07</v>
+        <v>12.30527</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>13.173221</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12412,7 +12416,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units, beginning of year $</t>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -12422,10 +12426,10 @@
         </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>12.30527</v>
+        <v>2.625389</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>13.173221</v>
+        <v>-0.590065</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12456,25 +12460,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.</t>
+          <t>Distributions to holders of redeemable units</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Increase (decrease) in net assets attributable to holders of redeemable units from operations</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>From net investment income</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetInvestmentIncome</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F157" s="5" t="n">
-        <v>2.625389</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>-0.590065</v>
+        <v>-0.137049</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12510,26 +12520,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>From net investment income</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>NetInvestmentIncome</t>
-        </is>
-      </c>
+          <t>Distributions to holders of redeemable units total</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F158" s="5" t="n">
+        <v>-0.596773</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>-0.137049</v>
+        <v>-0.546553</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12565,7 +12569,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Distributions to holders of redeemable units total</t>
+          <t>Net increase (decrease) in net assets attributable to holders of redeemable units for the year</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -12575,10 +12579,10 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-0.596773</v>
+        <v>0.867951</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>-0.546553</v>
+        <v>-2.147654</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12614,7 +12618,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in net assets attributable to holders of redeemable units for the year</t>
+          <t>Net assets attributable to holders of redeemable units, end of year $</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -12624,10 +12628,10 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.867951</v>
+        <v>13.173221</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>-2.147654</v>
+        <v>11.025567</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12663,7 +12667,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Net assets attributable to holders of redeemable units, end of year $</t>
+          <t>Distributions per unit $</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12673,10 +12677,10 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>13.173221</v>
+        <v>1.2e-07</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>11.025567</v>
+        <v>1.2e-07</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12694,55 +12698,6 @@
         </is>
       </c>
       <c r="K161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Distributions to holders of redeemable units</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Distributions per unit $</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/ENI.UN.xlsx
+++ b/output/pdf_financials_xlsx/ENI.UN.xlsx
@@ -1626,25 +1626,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.344356</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.641929</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.518339</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.405978</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.175821</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.430709</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.074796</v>
       </c>
     </row>
     <row r="35">
@@ -1682,25 +1682,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.344356</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.641929</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.518339</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.405978</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.175821</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.430709</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.074796</v>
       </c>
     </row>
     <row r="37">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
